--- a/MARKETS_SETUP_RATINGS.xlsx
+++ b/MARKETS_SETUP_RATINGS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\folam\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38586DB9-4A24-447C-B948-734D22657B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0F8485-2B03-46C8-B1DD-239E76F3CB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="11480" windowHeight="11370" xr2:uid="{C3316951-AD71-4EDD-9B99-4FF9EF3DF785}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{C3316951-AD71-4EDD-9B99-4FF9EF3DF785}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 US30" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,22 @@
     <sheet name="Financial Modelling " sheetId="6" r:id="rId3"/>
     <sheet name="README" sheetId="7" r:id="rId4"/>
     <sheet name="2025 US 30" sheetId="2" r:id="rId5"/>
-    <sheet name="2022 US 30" sheetId="4" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="Slicer_BUY_OR_SELL">#N/A</definedName>
+    <definedName name="Slicer_RATING">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
+      <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:slicerCache r:id="rId6"/>
+        <x14:slicerCache r:id="rId7"/>
+      </x15:slicerCaches>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -44,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="140">
   <si>
     <t>DATE</t>
   </si>
@@ -130,9 +142,6 @@
     <t xml:space="preserve">AGAINST 4HR WICK </t>
   </si>
   <si>
-    <t>NEWS WHILE IN TRADE</t>
-  </si>
-  <si>
     <t>MAY 13TH</t>
   </si>
   <si>
@@ -295,27 +304,6 @@
     <t>WIN</t>
   </si>
   <si>
-    <t>R:R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEC 22ND </t>
-  </si>
-  <si>
-    <t>DEC 1ST</t>
-  </si>
-  <si>
-    <t>NOV 16TH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOV 8TH </t>
-  </si>
-  <si>
-    <t>NOV 2ND</t>
-  </si>
-  <si>
-    <t>NOV 1ST</t>
-  </si>
-  <si>
     <t>RISK ON ALL TRADES</t>
   </si>
   <si>
@@ -391,58 +379,13 @@
     <t>16% INCREASE</t>
   </si>
   <si>
-    <t>OCT 20TH</t>
-  </si>
-  <si>
-    <t>OCT 19TH</t>
-  </si>
-  <si>
-    <t>SEP 23RD</t>
-  </si>
-  <si>
-    <t>SEP 16TH</t>
-  </si>
-  <si>
-    <t>SEP 8TH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEP 7TH </t>
-  </si>
-  <si>
-    <t>SEP 5TH</t>
-  </si>
-  <si>
-    <t>SEP 1ST</t>
-  </si>
-  <si>
-    <t>AUG 24TH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUG 9TH </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUG 4TH </t>
-  </si>
-  <si>
-    <t>AUG 1ST</t>
-  </si>
-  <si>
     <t>CUMULATIVE ROI</t>
   </si>
   <si>
     <t>Cumulative ROI</t>
   </si>
   <si>
-    <t>JULY 1ST</t>
-  </si>
-  <si>
-    <t>JUNE 29TH</t>
-  </si>
-  <si>
     <t>A*</t>
-  </si>
-  <si>
-    <t>JUNE 21ST</t>
   </si>
   <si>
     <t>Starting Capital</t>
@@ -543,7 +486,7 @@
     <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -600,14 +543,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -635,888 +637,13 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'2026 US30'!$E$46</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ADJ RISK PER TRADE WINS - LOSSES/ NET ROI</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-54A6-4EBB-90DD-466CECD8119D}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-54A6-4EBB-90DD-466CECD8119D}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-54A6-4EBB-90DD-466CECD8119D}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-54A6-4EBB-90DD-466CECD8119D}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dLbls>
-            <c:spPr>
-              <a:pattFill prst="pct75">
-                <a:fgClr>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:fgClr>
-                <a:bgClr>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:bgClr>
-              </a:pattFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="lt1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="9525">
-                  <a:solidFill>
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'2026 US30'!$D$47:$D$50</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>A TRADES</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>B TRADES</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>C TRADES</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>D&amp;F TRADES</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'2026 US30'!$E$47:$E$50</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.85000000000000009</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4B32-46F6-88DB-4D079779CE98}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="39000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="39000">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="lt1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="25000"/>
-          <a:lumOff val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'2026 US30'!$M$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Cumulative ROI</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'2026 US30'!$A$2:$A$25</c:f>
-              <c:strCache>
-                <c:ptCount val="24"/>
-                <c:pt idx="0">
-                  <c:v>JAN 6TH</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>JAN 15TH</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>FEB 4TH </c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>FEB 4TH </c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>FEB 12TH</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>MARCH 11TH</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>APRIL 2ND</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>APRIL 8TH</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>MAY 11TH</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>MAY 11TH</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>MAY 13TH</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>MAY 25TH </c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>MAY 27TH</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>MAY 29TH</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>JUNE 1ST</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>JUNE 9TH</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>JUNE 11TH</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>JUNE 11TH</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>JUNE 29TH </c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>JUNE 30TH </c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>JULY 31TH</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>AUGUST 5TH </c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>AUGUST 7TH </c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>SEPT 11TH</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'2026 US30'!$M$2:$M$25</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11.5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>10.5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>18.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>17.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>16.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6254-4845-8866-B25640775CBA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="2021818959"/>
-        <c:axId val="1912645103"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="0"/>
-                <c:order val="0"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'2026 US30'!$L$1</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>ROI</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="28575" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent1"/>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="none"/>
-                </c:marker>
-                <c:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'2026 US30'!$A$2:$A$25</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="24"/>
-                      <c:pt idx="0">
-                        <c:v>JAN 6TH</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>JAN 15TH</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>FEB 4TH </c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>FEB 4TH </c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>FEB 12TH</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>MARCH 11TH</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>APRIL 2ND</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>APRIL 8TH</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>MAY 11TH</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>MAY 11TH</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>MAY 13TH</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>MAY 25TH </c:v>
-                      </c:pt>
-                      <c:pt idx="12">
-                        <c:v>MAY 27TH</c:v>
-                      </c:pt>
-                      <c:pt idx="13">
-                        <c:v>MAY 29TH</c:v>
-                      </c:pt>
-                      <c:pt idx="14">
-                        <c:v>JUNE 1ST</c:v>
-                      </c:pt>
-                      <c:pt idx="15">
-                        <c:v>JUNE 9TH</c:v>
-                      </c:pt>
-                      <c:pt idx="16">
-                        <c:v>JUNE 11TH</c:v>
-                      </c:pt>
-                      <c:pt idx="17">
-                        <c:v>JUNE 11TH</c:v>
-                      </c:pt>
-                      <c:pt idx="18">
-                        <c:v>JUNE 29TH </c:v>
-                      </c:pt>
-                      <c:pt idx="19">
-                        <c:v>JUNE 30TH </c:v>
-                      </c:pt>
-                      <c:pt idx="20">
-                        <c:v>JULY 31TH</c:v>
-                      </c:pt>
-                      <c:pt idx="21">
-                        <c:v>AUGUST 5TH </c:v>
-                      </c:pt>
-                      <c:pt idx="22">
-                        <c:v>AUGUST 7TH </c:v>
-                      </c:pt>
-                      <c:pt idx="23">
-                        <c:v>SEPT 11TH</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'2026 US30'!$L$2:$L$25</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="24"/>
-                      <c:pt idx="0">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>3.5</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                      <c:pt idx="12">
-                        <c:v>3.5</c:v>
-                      </c:pt>
-                      <c:pt idx="13">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="14">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                      <c:pt idx="15">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                      <c:pt idx="16">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                      <c:pt idx="17">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="18">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                      <c:pt idx="19">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                      <c:pt idx="20">
-                        <c:v>2</c:v>
-                      </c:pt>
-                      <c:pt idx="21">
-                        <c:v>3.5</c:v>
-                      </c:pt>
-                      <c:pt idx="22">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                      <c:pt idx="23">
-                        <c:v>-1</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="0"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000000-6254-4845-8866-B25640775CBA}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-          </c:ext>
-        </c:extLst>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="2021818959"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1528,170 +655,14 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:r>
+              <a:rPr lang="en-CA" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>US30 Cumulative Performance ($100k Account)</a:t>
+            </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
-        </c:txPr>
-        <c:crossAx val="1912645103"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1912645103"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2021818959"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2341,7 +1312,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2645,7 +1616,426 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-CA" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Setup Rating Attribution</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-CA"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-CA"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2026 US30'!$E$46</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ADJ RISK PER TRADE WINS - LOSSES/ NET ROI</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-7F26-4696-AED2-B86C09D2D7C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-7F26-4696-AED2-B86C09D2D7C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-7F26-4696-AED2-B86C09D2D7C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-7F26-4696-AED2-B86C09D2D7C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'2026 US30'!$D$47:$D$50</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>A TRADES</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>B TRADES</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>C TRADES</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>D&amp;F TRADES</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2026 US30'!$E$47:$E$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.85000000000000009</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-7F26-4696-AED2-B86C09D2D7C9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3038,7 +2428,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3768,47 +3158,1026 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4409,1542 +4778,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -6545,7 +5379,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7066,92 +5900,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>445433</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>155202</xdr:rowOff>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>18142</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>242794</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>18676</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F619BA14-A7A9-B4CC-9733-C7B82C1E41FC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>211978</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>145863</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>572434</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>87592</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4F2C32D-25ED-4DB8-5960-FD6C43F0B943}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>18143</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1542142</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:colOff>598714</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7181,15 +5938,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>780143</xdr:colOff>
+      <xdr:colOff>780142</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>72571</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>526143</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>72572</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>417285</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7216,10 +5973,204 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>707571</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>145142</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F78F5C61-99E6-49A2-A1C8-85F49D618A6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>344714</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>72571</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>322943</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>151943</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="BUY OR SELL">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD09E95D-6107-4465-8ADC-2B60FCB1246E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="BUY OR SELL"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13081000" y="7329714"/>
+              <a:ext cx="1828800" cy="2619372"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-CA" sz="1100"/>
+                <a:t>This shape represents a table slicer. Table slicers are not supported in this version of Excel.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2007 or earlier, the slicer can't be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>507999</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>486227</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>79372</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="8" name="RATING">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5631C081-049B-4F10-B622-275EEE7B0691}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="RATING"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="15711713" y="7257143"/>
+              <a:ext cx="1828800" cy="2619372"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-CA" sz="1100"/>
+                <a:t>This shape represents a table slicer. Table slicers are not supported in this version of Excel.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2007 or earlier, the slicer can't be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -7294,6 +6245,65 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_BUY_OR_SELL" xr10:uid="{0CB67FB6-EA40-4471-82F3-AB315BC33B70}" sourceName="BUY OR SELL">
+  <extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
+      <x15:tableSlicerCache tableId="2" column="11"/>
+    </x:ext>
+  </extLst>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_RATING" xr10:uid="{FDFCD671-F61A-4E1B-BE83-2D211BDB0D33}" sourceName="RATING">
+  <extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
+      <x15:tableSlicerCache tableId="2" column="8"/>
+    </x:ext>
+  </extLst>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="BUY OR SELL" xr10:uid="{4963957D-B0F7-477B-B271-CDED3B7FEC86}" cache="Slicer_BUY_OR_SELL" caption="BUY OR SELL" rowHeight="251883"/>
+  <slicer name="RATING" xr10:uid="{A5D6D073-BA79-4634-B56F-A1822A8E47AC}" cache="Slicer_RATING" caption="RATING" rowHeight="251883"/>
+</slicers>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{49A98FD4-F8EC-4AF3-88A9-050B13726854}" name="Table1" displayName="Table1" ref="A1:O25" totalsRowShown="0">
+  <autoFilter ref="A1:O25" xr:uid="{49A98FD4-F8EC-4AF3-88A9-050B13726854}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{A4B7DF08-0FD5-4303-94BE-D47820EBBB95}" name="DATE"/>
+    <tableColumn id="2" xr3:uid="{7FEEAD53-87FD-4CC3-9830-4C729FFBC86E}" name="FVP  HIGH NODE"/>
+    <tableColumn id="3" xr3:uid="{7837C968-22B7-4EF4-BC7F-12CA348DA800}" name="FVP MED NODE"/>
+    <tableColumn id="4" xr3:uid="{BA14B132-D0EA-4EA1-A645-CC27DF370028}" name="FVP LOW NODE"/>
+    <tableColumn id="5" xr3:uid="{0304C1CA-2BE4-44B0-A17A-6AAFF7706EE4}" name="VWAP"/>
+    <tableColumn id="6" xr3:uid="{1C5A60E6-8B4F-4B5A-957B-A9B077339DCA}" name="WIN OR LOSS"/>
+    <tableColumn id="7" xr3:uid="{2DAC8A3E-7D64-40A9-93FB-FD5E5777E67D}" name="AGAINST 4HR WICK "/>
+    <tableColumn id="8" xr3:uid="{7C9C73D6-B560-448C-9FA6-27CB3A38D3FE}" name="RATING"/>
+    <tableColumn id="9" xr3:uid="{3B73EB17-ABF9-4473-9FC1-F7EED8903BF7}" name="ADJ RISK (XLOOKUP)" dataDxfId="3">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(IF(OR(H2="D", H2="F"), "D&amp;F TRADES", H2 &amp; " TRADES"), $C$32:$C$35, $A$32:$A$35, "N/A")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{E178BB3E-7E9C-4505-8DE9-48569B93CE24}" name="WIN RATE % (VLOOKUP)" dataDxfId="2" dataCellStyle="Percent">
+      <calculatedColumnFormula>VLOOKUP(IF(OR(H2="D", H2="F"), "D&amp;F TRADES", H2 &amp; " TRADES"), $C$32:$G$35, 5, FALSE)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{7CEB8733-42B6-4F8F-9119-A144510EA8EC}" name="BUY OR SELL"/>
+    <tableColumn id="12" xr3:uid="{1CD02414-5EE7-4899-B98F-63C92B11C328}" name="ROI"/>
+    <tableColumn id="13" xr3:uid="{9BD79FF6-C477-49CB-AFCA-1E24B8128D31}" name="Cumulative ROI">
+      <calculatedColumnFormula>M1+L2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{C471916E-805F-4722-B1E0-BA4138FCADA7}" name="TRADE PROFIT / LOSS" dataDxfId="1" dataCellStyle="Currency"/>
+    <tableColumn id="15" xr3:uid="{B57DFAA3-7D39-4302-AB46-1BE6FDEFA0AA}" name="ACCOUNT BALANCE" dataDxfId="0" dataCellStyle="Currency">
+      <calculatedColumnFormula>O1+N2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7617,18 +6627,18 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.81640625" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" customWidth="1"/>
-    <col min="3" max="3" width="18.08984375" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" customWidth="1"/>
+    <col min="3" max="3" width="22.54296875" customWidth="1"/>
     <col min="4" max="4" width="28.453125" customWidth="1"/>
     <col min="5" max="5" width="40.81640625" customWidth="1"/>
     <col min="6" max="6" width="27.08984375" customWidth="1"/>
-    <col min="7" max="7" width="16.1796875" customWidth="1"/>
+    <col min="7" max="7" width="27.7265625" customWidth="1"/>
     <col min="8" max="10" width="39" customWidth="1"/>
     <col min="11" max="11" width="21.26953125" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="49.90625" customWidth="1"/>
     <col min="14" max="14" width="35.6328125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="22.26953125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="30.26953125" style="2" customWidth="1"/>
     <col min="16" max="16" width="17.1796875" customWidth="1"/>
     <col min="17" max="17" width="19.54296875" customWidth="1"/>
   </cols>
@@ -7659,25 +6669,25 @@
         <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="J1" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="K1" t="s">
         <v>21</v>
       </c>
       <c r="L1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M1" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
@@ -7864,7 +6874,7 @@
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" si="0"/>
@@ -8104,7 +7114,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -8146,7 +7156,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -8169,7 +7179,7 @@
         <v>0.8</v>
       </c>
       <c r="K13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -8188,7 +7198,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -8230,7 +7240,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -8272,7 +7282,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -8314,7 +7324,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -8329,7 +7339,7 @@
         <v>7</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="0"/>
@@ -8359,7 +7369,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
@@ -8401,7 +7411,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
@@ -8443,7 +7453,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -8458,7 +7468,7 @@
         <v>7</v>
       </c>
       <c r="H20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I20" s="9">
         <f t="shared" si="0"/>
@@ -8488,7 +7498,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -8503,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="0"/>
@@ -8533,7 +7543,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -8575,7 +7585,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -8617,7 +7627,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
@@ -8659,7 +7669,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -8674,7 +7684,7 @@
         <v>7</v>
       </c>
       <c r="H25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="0"/>
@@ -8704,7 +7714,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="K27" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="L27">
         <f>SUM(L2:L25)</f>
@@ -8713,7 +7723,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="K28" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="L28">
         <f>L27-E36</f>
@@ -8722,34 +7732,34 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" t="s">
+        <v>66</v>
+      </c>
+      <c r="G31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" t="s">
+        <v>105</v>
+      </c>
+      <c r="K31" t="s">
         <v>82</v>
       </c>
-      <c r="F31" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31" t="s">
-        <v>79</v>
-      </c>
-      <c r="H31" t="s">
-        <v>113</v>
-      </c>
-      <c r="K31" t="s">
-        <v>90</v>
-      </c>
       <c r="L31" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M31" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
@@ -8760,7 +7770,7 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D32">
         <f>COUNTIF(H2:H25, "A" )</f>
@@ -8799,7 +7809,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D33">
         <f>COUNTIF(H2:H25, "B" )</f>
@@ -8838,7 +7848,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D34">
         <f>COUNTIF(H2:H25, "C" )</f>
@@ -8877,7 +7887,7 @@
         <v>0.1</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D35">
         <f>COUNTIF(H2:H25, "D" ) + COUNTIF(H2:H25, "F")</f>
@@ -8910,7 +7920,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C36" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <f>SUM(D32:D35)</f>
@@ -8933,14 +7943,14 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="E39" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F39">
         <f>E36/D36*100</f>
         <v>50</v>
       </c>
       <c r="K39" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="L39">
         <f>SUM(L32:L35)</f>
@@ -8949,19 +7959,19 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G40" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="E41" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F41">
         <f>E37/D37*100</f>
         <v>66.666666666666657</v>
       </c>
       <c r="K41" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="L41">
         <f>L39-L28</f>
@@ -8970,15 +7980,15 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D46" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E46" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E47">
         <f>H32*B32-F32*B32</f>
@@ -8987,7 +7997,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E48">
         <f>H33*B33-F33*B33</f>
@@ -8996,7 +8006,7 @@
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.35">
       <c r="D49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E49">
         <f>H34*B34-F34*B34</f>
@@ -9005,7 +8015,7 @@
     </row>
     <row r="50" spans="4:5" x14ac:dyDescent="0.35">
       <c r="D50" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E50">
         <f>H35*B35-F35*B35</f>
@@ -9014,7 +8024,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -9032,16 +8044,16 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="H2" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.35">
@@ -9062,6 +8074,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{3A4CF648-6AED-40f4-86FF-DC5316D8AED3}">
+      <x14:slicerList xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -9078,7 +8097,7 @@
   <sheetData>
     <row r="2" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="D2" s="2">
         <v>100000</v>
@@ -9086,7 +8105,7 @@
     </row>
     <row r="3" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D3" s="3">
         <v>0.01</v>
@@ -9094,7 +8113,7 @@
     </row>
     <row r="4" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="D4" s="4">
         <f>D2*D3</f>
@@ -9103,39 +8122,39 @@
     </row>
     <row r="5" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J12" t="s">
         <v>82</v>
       </c>
-      <c r="G12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I12" t="s">
-        <v>113</v>
-      </c>
-      <c r="J12" t="s">
-        <v>90</v>
-      </c>
       <c r="K12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="L12" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="3:12" x14ac:dyDescent="0.35">
@@ -9143,7 +8162,7 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13">
         <f>COUNTIF('2026 US30'!H:H, "A")</f>
@@ -9179,7 +8198,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14">
         <f>COUNTIF('2026 US30'!H:H, "B")</f>
@@ -9215,7 +8234,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15">
         <f>COUNTIF('2026 US30'!H:H, "C")</f>
@@ -9251,7 +8270,7 @@
         <v>0.1</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E16">
         <f>COUNTIF('2026 US30'!H:H, "D") + COUNTIF('2026 US30'!H:H, "F")</f>
@@ -9284,7 +8303,7 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="C18">
         <f>'2026 US30'!O25</f>
@@ -9293,7 +8312,7 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="C19" s="4">
         <f>$D$2+((I13+I14+I15)*$D$4)</f>
@@ -9303,7 +8322,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="C20" s="4">
         <f>C18-(0.1*SUM(E13:E16)*$D$4)</f>
@@ -9325,7 +8344,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -9340,7 +8359,7 @@
     </row>
     <row r="2" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -9355,7 +8374,7 @@
     </row>
     <row r="3" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -9383,7 +8402,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -9398,7 +8417,7 @@
     </row>
     <row r="6" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -9413,7 +8432,7 @@
     </row>
     <row r="7" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -9428,7 +8447,7 @@
     </row>
     <row r="8" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -9456,7 +8475,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -9471,7 +8490,7 @@
     </row>
     <row r="11" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -9486,7 +8505,7 @@
     </row>
     <row r="12" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -9501,7 +8520,7 @@
     </row>
     <row r="13" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -9516,7 +8535,7 @@
     </row>
     <row r="14" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -9544,7 +8563,7 @@
     </row>
     <row r="16" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -9559,7 +8578,7 @@
     </row>
     <row r="17" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -9574,7 +8593,7 @@
     </row>
     <row r="18" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -9589,7 +8608,7 @@
     </row>
     <row r="19" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -9680,15 +8699,15 @@
         <v>21</v>
       </c>
       <c r="J1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K1" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -9700,7 +8719,7 @@
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -9715,7 +8734,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -9742,7 +8761,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -9757,7 +8776,7 @@
         <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
@@ -9772,7 +8791,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -9799,7 +8818,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -9826,7 +8845,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -9853,7 +8872,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -9880,7 +8899,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -9907,7 +8926,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -9934,7 +8953,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -9961,7 +8980,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -9988,7 +9007,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
@@ -10015,7 +9034,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -10042,7 +9061,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -10072,7 +9091,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -10102,7 +9121,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -10129,7 +9148,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
@@ -10156,7 +9175,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
@@ -10183,7 +9202,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -10210,7 +9229,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -10237,7 +9256,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
@@ -10267,7 +9286,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -10294,7 +9313,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -10321,7 +9340,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
@@ -10348,7 +9367,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -10375,7 +9394,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -10402,7 +9421,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -10432,7 +9451,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
@@ -10459,7 +9478,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
@@ -10486,7 +9505,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -10501,7 +9520,7 @@
         <v>7</v>
       </c>
       <c r="H31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I31" t="s">
         <v>22</v>
@@ -10516,7 +9535,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -10543,7 +9562,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B33" t="s">
         <v>7</v>
@@ -10570,7 +9589,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
         <v>7</v>
@@ -10597,7 +9616,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -10624,7 +9643,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
@@ -10651,7 +9670,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -10678,7 +9697,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -10705,7 +9724,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -10732,7 +9751,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="I46" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="J46">
         <f>SUM(J2:J39)</f>
@@ -10741,7 +9760,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="I47" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J47">
         <f>J46-16</f>
@@ -10750,33 +9769,33 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="I49" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="J49" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.35">
@@ -10784,7 +9803,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D50">
         <f>COUNTIF(H2:H39, "A" )</f>
@@ -10820,7 +9839,7 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D51">
         <f>COUNTIF(H2:H39, "B")</f>
@@ -10856,7 +9875,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D52">
         <f>COUNTIF(H2:H39, "C" )</f>
@@ -10892,7 +9911,7 @@
         <v>0.1</v>
       </c>
       <c r="C53" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D53">
         <f>COUNTIF(H2:H39, "D" ) + COUNTIF(H2:H39, "F")</f>
@@ -10945,14 +9964,14 @@
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.35">
       <c r="E56" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F56">
         <f>E54/D54*100</f>
         <v>56.756756756756758</v>
       </c>
       <c r="I56" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J56">
         <f>SUM(J50:J53)</f>
@@ -10961,14 +9980,14 @@
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.35">
       <c r="E58" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F58">
         <f>E55/D55*100</f>
         <v>68</v>
       </c>
       <c r="I58" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="J58">
         <f>J56-J47</f>
@@ -10977,15 +9996,15 @@
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D63" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E63" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E64">
         <f>H50*B50-B50*F50</f>
@@ -10994,7 +10013,7 @@
     </row>
     <row r="65" spans="4:5" x14ac:dyDescent="0.35">
       <c r="D65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E65">
         <f>H51*B51-B51*F51</f>
@@ -11003,7 +10022,7 @@
     </row>
     <row r="66" spans="4:5" x14ac:dyDescent="0.35">
       <c r="D66" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E66">
         <f>H52*B52-B52*F52</f>
@@ -11012,7 +10031,7 @@
     </row>
     <row r="67" spans="4:5" x14ac:dyDescent="0.35">
       <c r="D67" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E67">
         <f>H53*B53-B53*F53</f>
@@ -11023,558 +10042,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{275AE848-0AC0-4AC3-A58A-C688ACF14240}">
-  <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.26953125" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" customWidth="1"/>
-    <col min="3" max="3" width="14.54296875" customWidth="1"/>
-    <col min="4" max="4" width="15.54296875" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" customWidth="1"/>
-    <col min="7" max="7" width="17.7265625" customWidth="1"/>
-    <col min="9" max="10" width="13.6328125" customWidth="1"/>
-    <col min="11" max="11" width="27.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" t="s">
-        <v>83</v>
-      </c>
-      <c r="K1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>122</v>
-      </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>8</v>
-      </c>
-      <c r="H16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" t="s">
-        <v>7</v>
-      </c>
-      <c r="H18" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>125</v>
-      </c>
-      <c r="D19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>126</v>
-      </c>
-      <c r="B20" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>132</v>
-      </c>
-      <c r="B24" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>